--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251002_170450.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251002_170450.xlsx
@@ -5152,7 +5152,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251002_170450.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251002_170450.xlsx
@@ -5152,7 +5152,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
